--- a/output/pdf_financials_xlsx/SMY.xlsx
+++ b/output/pdf_financials_xlsx/SMY.xlsx
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001892</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002702</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.049613</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.008603</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000465</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000691</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002169</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1906,28 +1906,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.593282</v>
+        <v>-0.595174</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.21767</v>
+        <v>-3.220372</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.433616</v>
+        <v>-3.483229</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.914578</v>
+        <v>-6.923181</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.824234</v>
+        <v>-2.824699</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.373551</v>
+        <v>-1.374242</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.300968</v>
+        <v>0.298799</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.41389</v>
+        <v>-0.413893</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.885557</v>
@@ -2016,28 +2016,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.593282</v>
+        <v>-0.595174</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.21767</v>
+        <v>-3.220372</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.433616</v>
+        <v>-3.483229</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.914578</v>
+        <v>-6.923181</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.824234</v>
+        <v>-2.824699</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.373551</v>
+        <v>-1.374242</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.300968</v>
+        <v>0.298799</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.41389</v>
+        <v>-0.413893</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.885557</v>
@@ -2322,37 +2322,37 @@
         <v>0.08597399999999999</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.594121</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.406852</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.391412</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.293508</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.063848</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.228101</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.618223</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.457537</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.007292</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.456301</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.431465</v>
       </c>
     </row>
     <row r="35">
@@ -2432,37 +2432,37 @@
         <v>0.08597399999999999</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.594121</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.105</v>
+        <v>0.511852</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.391412</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.293508</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.063848</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.228101</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.618223</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.457537</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.007292</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.456301</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.431465</v>
       </c>
     </row>
     <row r="37">
@@ -3092,37 +3092,37 @@
         <v>0.054978</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.720766</v>
+        <v>0.126645</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.489278</v>
+        <v>0.082426</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.492897</v>
+        <v>0.101485</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.327468</v>
+        <v>0.03396</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.067542</v>
+        <v>0.003694</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.281901</v>
+        <v>0.0538</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.853734</v>
+        <v>0.235511</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.534228</v>
+        <v>0.076691</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.021031</v>
+        <v>0.013739</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.485791</v>
+        <v>0.02949</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.44906</v>
+        <v>0.017595</v>
       </c>
     </row>
     <row r="49">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8610,7 +8610,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -16308,7 +16312,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -16960,7 +16964,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -17906,7 +17914,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -18400,7 +18408,11 @@
           <t>Reclamation deposits 50,000</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -37624,7 +37636,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -42050,7 +42066,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -44140,7 +44156,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -45066,7 +45082,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -45812,7 +45828,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -46772,7 +46788,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E416" s="5" t="n">

--- a/output/pdf_financials_xlsx/SMY.xlsx
+++ b/output/pdf_financials_xlsx/SMY.xlsx
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.440655</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>3.969004</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -40212,7 +40212,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E344" s="5" t="n">
         <v>0.440655</v>
       </c>

--- a/output/pdf_financials_xlsx/SMY.xlsx
+++ b/output/pdf_financials_xlsx/SMY.xlsx
@@ -727,43 +727,43 @@
         <v>0.140309</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.526081</v>
+        <v>0.5620810000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.804003</v>
+        <v>0.8460029999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.7964830000000001</v>
+        <v>0.871483</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.067972</v>
+        <v>1.142972</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.323796</v>
+        <v>1.391296</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.590592</v>
+        <v>0.6445920000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.667923</v>
+        <v>0.721923</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.697262</v>
+        <v>0.760262</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.454709</v>
+        <v>0.511709</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.442708</v>
+        <v>0.496708</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.817001</v>
+        <v>0.902501</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.920111</v>
+        <v>1.058111</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.976438</v>
+        <v>1.100438</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.39772</v>
@@ -892,43 +892,43 @@
         <v>0.140309</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.526081</v>
+        <v>0.5620810000000001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.804003</v>
+        <v>0.8460029999999999</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.7964830000000001</v>
+        <v>0.871483</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.067972</v>
+        <v>1.142972</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.323796</v>
+        <v>1.391296</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.590592</v>
+        <v>0.6445920000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.667923</v>
+        <v>0.721923</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.697262</v>
+        <v>0.760262</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.454709</v>
+        <v>0.511709</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.442708</v>
+        <v>0.496708</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.817001</v>
+        <v>0.902501</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.920111</v>
+        <v>1.058111</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.976438</v>
+        <v>1.100438</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.39772</v>
@@ -947,43 +947,43 @@
         <v>-0.140309</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.526081</v>
+        <v>-0.5620810000000001</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.804003</v>
+        <v>-0.8460029999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.7964830000000001</v>
+        <v>-0.871483</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.067972</v>
+        <v>-1.142972</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-1.323796</v>
+        <v>-1.391296</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.590592</v>
+        <v>-0.6445920000000001</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.667923</v>
+        <v>-0.721923</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.697262</v>
+        <v>-0.760262</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.454709</v>
+        <v>-0.511709</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.442708</v>
+        <v>-0.496708</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.817001</v>
+        <v>-0.902501</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.920111</v>
+        <v>-1.058111</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.976438</v>
+        <v>-1.100438</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>-0.39772</v>
@@ -3582,19 +3582,19 @@
         <v>0</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>0.76563</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>1.400728</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>1.226551</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>1.226551</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>1.226551</v>
       </c>
     </row>
     <row r="57">
@@ -3637,19 +3637,19 @@
         <v>0</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>0.431369</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>0.596907</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>0.763286</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>0.884661</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>0.973448</v>
       </c>
     </row>
     <row r="58">
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.527375</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.944906</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.468499</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.420811</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0.880414</v>
@@ -4055,10 +4055,10 @@
         <v>2.941095</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>3.133616</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>2.930483</v>
       </c>
     </row>
     <row r="65">
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.427337</v>
+        <v>-0.695581</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.325935</v>
+        <v>-0.421733</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0.730525</v>
@@ -6599,16 +6599,16 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.010707</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.033271</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.07727299999999999</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.014443</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -6617,10 +6617,10 @@
         <v>0</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.011605</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.10646</v>
       </c>
     </row>
     <row r="111">
@@ -6630,19 +6630,19 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002214</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.147036</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.220275</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003315</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00213</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -6657,10 +6657,10 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002457</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>-0.363484</v>
@@ -6853,13 +6853,13 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.073564</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.231125</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.397191</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.197123</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -7929,19 +7929,19 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002214</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.147036</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.220275</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003315</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00213</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -7956,10 +7956,10 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002457</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>-0.363484</v>
@@ -7989,16 +7989,16 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.122589</v>
+        <v>-1.269625</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.628564</v>
+        <v>-1.848839</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.017699</v>
+        <v>-1.021014</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.693696</v>
+        <v>-0.6958259999999999</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.760982</v>
@@ -8013,10 +8013,10 @@
         <v>-0.697159</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.46611</v>
+        <v>-0.468567</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.6147319999999999</v>
+        <v>-0.648732</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-2.201955</v>
@@ -24502,7 +24502,11 @@
           <t>Accretion 10</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -29146,7 +29150,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -30412,7 +30420,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -31622,7 +31634,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -34840,7 +34856,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -35200,7 +35220,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -36792,7 +36816,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -37446,7 +37474,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -38688,7 +38720,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E328" s="5" t="n">
         <v>-0.15</v>
       </c>
@@ -38972,7 +39008,11 @@
           <t>HST/GST recoverable</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -39834,7 +39874,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -39930,7 +39974,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E341" s="5" t="n">
         <v>-0.002214</v>
       </c>
@@ -43060,7 +43108,11 @@
           <t>Non-executive directors fees 13</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -44624,7 +44676,11 @@
           <t>Non-executive directors fees 12</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -47826,7 +47882,11 @@
           <t>Non-executive directors fees 14</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -52298,7 +52358,11 @@
           <t>Non-executive directors fees (Note 9)</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -54390,7 +54454,11 @@
           <t>Future income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E496" s="5" t="n">
         <v>0.15</v>
       </c>
